--- a/evaluations/classification/classification_results_global_embedding.xlsx
+++ b/evaluations/classification/classification_results_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>F-1 Score</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Use Shape</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Dataset Type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -605,6 +615,8 @@
       <c r="U2" t="n">
         <v>0.8248</v>
       </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -676,6 +688,8 @@
       <c r="U3" t="n">
         <v>0.883</v>
       </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -747,6 +761,8 @@
       <c r="U4" t="n">
         <v>0.052</v>
       </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -818,6 +834,8 @@
       <c r="U5" t="n">
         <v>0.08699999999999999</v>
       </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -889,6 +907,8 @@
       <c r="U6" t="n">
         <v>0.9474</v>
       </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -960,6 +980,8 @@
       <c r="U7" t="n">
         <v>0.9847</v>
       </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1031,6 +1053,8 @@
       <c r="U8" t="n">
         <v>0.5244</v>
       </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1102,6 +1126,8 @@
       <c r="U9" t="n">
         <v>0.484</v>
       </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1173,6 +1199,8 @@
       <c r="U10" t="n">
         <v>0.6079</v>
       </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1244,6 +1272,8 @@
       <c r="U11" t="n">
         <v>0.5302</v>
       </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1315,6 +1345,8 @@
       <c r="U12" t="n">
         <v>0.6287</v>
       </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1386,6 +1418,8 @@
       <c r="U13" t="n">
         <v>0.8038</v>
       </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1457,6 +1491,8 @@
       <c r="U14" t="n">
         <v>0.1345</v>
       </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1528,18 +1564,20 @@
       <c r="U15" t="n">
         <v>0.1318</v>
       </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1547,13 +1585,13 @@
         </is>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
       <c r="G16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>256</v>
@@ -1588,29 +1626,37 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.68</v>
+        <v>6.91</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6545</v>
+        <v>0.1503</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7276</v>
+        <v>0.3671</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6428</v>
+        <v>0.1288</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C17" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1618,7 +1664,7 @@
         </is>
       </c>
       <c r="E17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -1659,29 +1705,37 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.44</v>
+        <v>9.98</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7907</v>
+        <v>0.1503</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8738</v>
+        <v>0.3671</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7712</v>
+        <v>0.1288</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>SealID</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>655</v>
+        <v>1668</v>
       </c>
       <c r="C18" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1695,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>256</v>
@@ -1730,29 +1784,31 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.73</v>
+        <v>5.68</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9826</v>
+        <v>0.6545</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0.7276</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9797</v>
-      </c>
+        <v>0.6428</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>SealID</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>655</v>
+        <v>1668</v>
       </c>
       <c r="C19" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1766,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>256</v>
@@ -1801,17 +1857,165 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7907</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.8738</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>655</v>
+      </c>
+      <c r="C20" t="n">
+        <v>43</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>256</v>
+      </c>
+      <c r="I20" t="n">
+        <v>128</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>50</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>655</v>
+      </c>
+      <c r="C21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>256</v>
+      </c>
+      <c r="I21" t="n">
+        <v>128</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.54</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S21" t="n">
         <v>0.9391</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>0.9478</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U21" t="n">
         <v>0.9331</v>
       </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/evaluations/classification/classification_results_global_embedding.xlsx
+++ b/evaluations/classification/classification_results_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,14 +1728,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
       <c r="G18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>256</v>
@@ -1769,7 +1769,7 @@
         <v>0.35</v>
       </c>
       <c r="M18" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>10</v>
@@ -1784,31 +1784,37 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>5.68</v>
+        <v>7.34</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6545</v>
+        <v>0.1879</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7276</v>
+        <v>0.3006</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6428</v>
-      </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+        <v>0.1645</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1816,7 +1822,7 @@
         </is>
       </c>
       <c r="E19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -1857,31 +1863,37 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>5.44</v>
+        <v>8.77</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7907</v>
+        <v>0.2514</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8738</v>
+        <v>0.3815</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7712</v>
-      </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+        <v>0.2139</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>SealID</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>655</v>
+        <v>1668</v>
       </c>
       <c r="C20" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1895,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>256</v>
@@ -1930,16 +1942,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>5.68</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9826</v>
+        <v>0.6545</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>0.7276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9797</v>
+        <v>0.6428</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
@@ -1947,14 +1959,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>SealID</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>655</v>
+        <v>1668</v>
       </c>
       <c r="C21" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1968,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>256</v>
@@ -2003,19 +2015,165 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.54</v>
+        <v>5.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9391</v>
+        <v>0.7907</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9478</v>
+        <v>0.8738</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9331</v>
+        <v>0.7712</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>655</v>
+      </c>
+      <c r="C22" t="n">
+        <v>43</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>256</v>
+      </c>
+      <c r="I22" t="n">
+        <v>128</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>655</v>
+      </c>
+      <c r="C23" t="n">
+        <v>43</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>256</v>
+      </c>
+      <c r="I23" t="n">
+        <v>128</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>50</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9391</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.9478</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/evaluations/classification/classification_results_global_embedding.xlsx
+++ b/evaluations/classification/classification_results_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>256</v>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>8.48</v>
+        <v>8.85</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5609</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7395</v>
+        <v>0.6555</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6079</v>
+        <v>0.5302</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>256</v>
@@ -1261,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>8.85</v>
+        <v>8.48</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5609</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6555</v>
+        <v>0.7395</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5302</v>
+        <v>0.6079</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -1480,19 +1480,25 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>7.17</v>
+        <v>42.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.159</v>
+        <v>0.1503</v>
       </c>
       <c r="T14" t="n">
         <v>0.289</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1345</v>
-      </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+        <v>0.1213</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1512,7 +1518,7 @@
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -1553,19 +1559,25 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.84</v>
+        <v>9.98</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1532</v>
+        <v>0.1503</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3786</v>
+        <v>0.3671</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1318</v>
-      </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+        <v>0.1288</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1594,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>128</v>
@@ -1611,7 +1623,7 @@
         <v>0.35</v>
       </c>
       <c r="M16" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>10</v>
@@ -1626,19 +1638,19 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>6.91</v>
+        <v>1.09</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1503</v>
+        <v>0.0896</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3671</v>
+        <v>0.185</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1288</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1660,20 +1672,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E17" t="b">
         <v>1</v>
       </c>
       <c r="F17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>128</v>
@@ -1690,7 +1702,7 @@
         <v>0.35</v>
       </c>
       <c r="M17" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
         <v>10</v>
@@ -1705,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>9.98</v>
+        <v>5.75</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1503</v>
+        <v>0.1185</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3671</v>
+        <v>0.2283</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1288</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
@@ -1769,7 +1781,7 @@
         <v>0.35</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N18" t="n">
         <v>10</v>
@@ -1784,19 +1796,19 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7.34</v>
+        <v>8.77</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1879</v>
+        <v>0.2514</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3006</v>
+        <v>0.3815</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1645</v>
+        <v>0.2139</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -1848,7 +1860,7 @@
         <v>0.35</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
         <v>10</v>
@@ -1863,19 +1875,19 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>8.77</v>
+        <v>7.34</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2514</v>
+        <v>0.1879</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3815</v>
+        <v>0.3006</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2139</v>
+        <v>0.1645</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -1886,14 +1898,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C20" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1901,16 +1913,16 @@
         </is>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
         <v>128</v>
@@ -1927,7 +1939,7 @@
         <v>0.35</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N20" t="n">
         <v>10</v>
@@ -1942,31 +1954,37 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.68</v>
+        <v>1.98</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6545</v>
+        <v>0.0896</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7276</v>
+        <v>0.185</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6428</v>
-      </c>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1974,7 +1992,7 @@
         </is>
       </c>
       <c r="E21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -2015,31 +2033,37 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.44</v>
+        <v>6.91</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7907</v>
+        <v>0.1503</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8738</v>
+        <v>0.3671</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7712</v>
-      </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+        <v>0.1288</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>655</v>
+        <v>1498</v>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2088,16 +2112,16 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.73</v>
+        <v>6.84</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9826</v>
+        <v>0.1532</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0.3786</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9797</v>
+        <v>0.1318</v>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
@@ -2105,75 +2129,604 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C23" t="n">
+        <v>227</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>128</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C24" t="n">
+        <v>227</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>128</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.08409999999999999</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C25" t="n">
+        <v>227</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>256</v>
+      </c>
+      <c r="I25" t="n">
+        <v>128</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M25" t="n">
+        <v>50</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C26" t="n">
+        <v>227</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>256</v>
+      </c>
+      <c r="I26" t="n">
+        <v>128</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M26" t="n">
+        <v>50</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C27" t="n">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>256</v>
+      </c>
+      <c r="I27" t="n">
+        <v>128</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M27" t="n">
+        <v>50</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.7276</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C28" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>256</v>
+      </c>
+      <c r="I28" t="n">
+        <v>128</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M28" t="n">
+        <v>50</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.7907</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.8738</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>StripeSpotter</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B29" t="n">
         <v>655</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C29" t="n">
         <v>43</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>ensamble</t>
         </is>
       </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
         <v>256</v>
       </c>
-      <c r="I23" t="n">
-        <v>128</v>
-      </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="I29" t="n">
+        <v>128</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M29" t="n">
         <v>50</v>
       </c>
-      <c r="N23" t="n">
-        <v>10</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
         <v>1.54</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S29" t="n">
         <v>0.9391</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T29" t="n">
         <v>0.9478</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U29" t="n">
         <v>0.9331</v>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>655</v>
+      </c>
+      <c r="C30" t="n">
+        <v>43</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>256</v>
+      </c>
+      <c r="I30" t="n">
+        <v>128</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>50</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/evaluations/classification/classification_results_global_embedding.xlsx
+++ b/evaluations/classification/classification_results_global_embedding.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>256</v>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>8.85</v>
+        <v>8.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5609</v>
+        <v>0.6366000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6555</v>
+        <v>0.7395</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5302</v>
+        <v>0.6079</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>256</v>
@@ -1261,16 +1261,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>8.48</v>
+        <v>8.85</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5609</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7395</v>
+        <v>0.6555</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6079</v>
+        <v>0.5302</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -1435,14 +1435,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E14" t="b">
         <v>1</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -1480,16 +1480,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>42.1</v>
+        <v>6.24</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1503</v>
+        <v>0.2254</v>
       </c>
       <c r="T14" t="n">
-        <v>0.289</v>
+        <v>0.3526</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1213</v>
+        <v>0.2024</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9.98</v>
+        <v>8.77</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1503</v>
+        <v>0.2514</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3671</v>
+        <v>0.3815</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1288</v>
+        <v>0.2139</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1603,10 +1603,10 @@
         <v>0</v>
       </c>
       <c r="G16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="I16" t="n">
         <v>128</v>
@@ -1623,7 +1623,7 @@
         <v>0.35</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N16" t="n">
         <v>10</v>
@@ -1638,19 +1638,19 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.09</v>
+        <v>6.05</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0896</v>
+        <v>0.2081</v>
       </c>
       <c r="T16" t="n">
-        <v>0.185</v>
+        <v>0.341</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1854</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -1679,13 +1679,13 @@
         <v>1</v>
       </c>
       <c r="F17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="I17" t="n">
         <v>128</v>
@@ -1702,7 +1702,7 @@
         <v>0.35</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N17" t="n">
         <v>10</v>
@@ -1717,19 +1717,19 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.75</v>
+        <v>5.31</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1185</v>
+        <v>0.1329</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2283</v>
+        <v>0.2399</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -1758,13 +1758,13 @@
         <v>1</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>128</v>
@@ -1781,7 +1781,7 @@
         <v>0.35</v>
       </c>
       <c r="M18" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
         <v>10</v>
@@ -1796,16 +1796,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>8.77</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2514</v>
+        <v>0.104</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3815</v>
+        <v>0.2023</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2139</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E19" t="b">
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>256</v>
@@ -1860,7 +1860,7 @@
         <v>0.35</v>
       </c>
       <c r="M19" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
         <v>10</v>
@@ -1875,19 +1875,19 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>7.34</v>
+        <v>5.76</v>
       </c>
       <c r="S19" t="n">
         <v>0.1879</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3006</v>
+        <v>0.2803</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1645</v>
+        <v>0.1509</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="I20" t="n">
         <v>128</v>
@@ -1939,7 +1939,7 @@
         <v>0.35</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
         <v>10</v>
@@ -1954,16 +1954,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.98</v>
+        <v>42.1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0896</v>
+        <v>0.1503</v>
       </c>
       <c r="T20" t="n">
-        <v>0.185</v>
+        <v>0.289</v>
       </c>
       <c r="U20" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1213</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -2033,25 +2033,19 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.91</v>
+        <v>6.84</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1503</v>
+        <v>0.1532</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3671</v>
+        <v>0.3786</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1288</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>WildlifeReID10k</t>
-        </is>
-      </c>
+        <v>0.1318</v>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2067,11 +2061,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -2112,19 +2106,25 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>6.84</v>
+        <v>5.99</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1532</v>
+        <v>0.2081</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3786</v>
+        <v>0.341</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1318</v>
-      </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+        <v>0.1854</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2147,13 +2147,13 @@
         <v>1</v>
       </c>
       <c r="F23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="I23" t="n">
         <v>128</v>
@@ -2170,7 +2170,7 @@
         <v>0.35</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="N23" t="n">
         <v>10</v>
@@ -2185,16 +2185,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>26.6</v>
+        <v>6.91</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1012</v>
+        <v>0.1503</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2283</v>
+        <v>0.3671</v>
       </c>
       <c r="U23" t="n">
-        <v>0.075</v>
+        <v>0.1288</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
@@ -2264,16 +2264,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>26.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0.104</v>
+        <v>0.1012</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2023</v>
+        <v>0.2283</v>
       </c>
       <c r="U24" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.075</v>
       </c>
       <c r="V24" t="n">
         <v>1</v>
@@ -2302,13 +2302,13 @@
         </is>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
       <c r="G25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>256</v>
@@ -2328,7 +2328,7 @@
         <v>0.35</v>
       </c>
       <c r="M25" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
         <v>10</v>
@@ -2343,19 +2343,25 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>7.17</v>
+        <v>7.34</v>
       </c>
       <c r="S25" t="n">
-        <v>0.159</v>
+        <v>0.1879</v>
       </c>
       <c r="T25" t="n">
-        <v>0.289</v>
+        <v>0.3006</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1345</v>
-      </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+        <v>0.1645</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2371,7 +2377,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>disk</t>
+          <t>ensamble</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -2416,19 +2422,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.99</v>
+        <v>9.98</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2081</v>
+        <v>0.1503</v>
       </c>
       <c r="T26" t="n">
-        <v>0.341</v>
+        <v>0.3671</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1854</v>
+        <v>0.1288</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -2439,14 +2445,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C27" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2454,16 +2460,16 @@
         </is>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>128</v>
@@ -2480,7 +2486,7 @@
         <v>0.35</v>
       </c>
       <c r="M27" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N27" t="n">
         <v>10</v>
@@ -2495,45 +2501,51 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5.68</v>
+        <v>1.98</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6545</v>
+        <v>0.0896</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7276</v>
+        <v>0.185</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6428</v>
-      </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SealID</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1668</v>
+        <v>1498</v>
       </c>
       <c r="C28" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
       </c>
       <c r="G28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>256</v>
@@ -2568,48 +2580,54 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5.44</v>
+        <v>6.02</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7907</v>
+        <v>0.2081</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8738</v>
+        <v>0.3295</v>
       </c>
       <c r="U28" t="n">
-        <v>0.7712</v>
-      </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+        <v>0.1858</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>655</v>
+        <v>1498</v>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ensamble</t>
+          <t>disk</t>
         </is>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>128</v>
@@ -2626,7 +2644,7 @@
         <v>0.35</v>
       </c>
       <c r="M29" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
         <v>10</v>
@@ -2641,31 +2659,37 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.54</v>
+        <v>5.75</v>
       </c>
       <c r="S29" t="n">
-        <v>0.9391</v>
+        <v>0.1185</v>
       </c>
       <c r="T29" t="n">
-        <v>0.9478</v>
+        <v>0.2283</v>
       </c>
       <c r="U29" t="n">
-        <v>0.9331</v>
-      </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>StripeSpotter</t>
+          <t>NyalaData</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>655</v>
+        <v>1498</v>
       </c>
       <c r="C30" t="n">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2679,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>256</v>
@@ -2714,19 +2738,706 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.73</v>
+        <v>7.17</v>
       </c>
       <c r="S30" t="n">
-        <v>0.9826</v>
+        <v>0.159</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0.289</v>
       </c>
       <c r="U30" t="n">
-        <v>0.9797</v>
+        <v>0.1345</v>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C31" t="n">
+        <v>227</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>256</v>
+      </c>
+      <c r="I31" t="n">
+        <v>128</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M31" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.1385</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C32" t="n">
+        <v>227</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>128</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.07049999999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C33" t="n">
+        <v>227</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>disk</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>256</v>
+      </c>
+      <c r="I33" t="n">
+        <v>128</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M33" t="n">
+        <v>50</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2254</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C34" t="n">
+        <v>227</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>256</v>
+      </c>
+      <c r="I34" t="n">
+        <v>128</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M34" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NyalaData</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1498</v>
+      </c>
+      <c r="C35" t="n">
+        <v>227</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>256</v>
+      </c>
+      <c r="I35" t="n">
+        <v>128</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M35" t="n">
+        <v>50</v>
+      </c>
+      <c r="N35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2283</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C36" t="n">
+        <v>55</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>256</v>
+      </c>
+      <c r="I36" t="n">
+        <v>128</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M36" t="n">
+        <v>50</v>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.7276</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SealID</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1668</v>
+      </c>
+      <c r="C37" t="n">
+        <v>55</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>256</v>
+      </c>
+      <c r="I37" t="n">
+        <v>128</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M37" t="n">
+        <v>50</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.7907</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.8738</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>655</v>
+      </c>
+      <c r="C38" t="n">
+        <v>43</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>256</v>
+      </c>
+      <c r="I38" t="n">
+        <v>128</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M38" t="n">
+        <v>50</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>StripeSpotter</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>655</v>
+      </c>
+      <c r="C39" t="n">
+        <v>43</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="n">
+        <v>256</v>
+      </c>
+      <c r="I39" t="n">
+        <v>128</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M39" t="n">
+        <v>50</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.9391</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.9478</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
